--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.16945594980679</v>
+        <v>2.302536591843603</v>
       </c>
       <c r="D2" t="n">
-        <v>27.15113324652287</v>
+        <v>4.412059152559967</v>
       </c>
       <c r="E2" t="n">
-        <v>14.21492039917519</v>
+        <v>2.309924564865969</v>
       </c>
       <c r="F2" t="n">
-        <v>12.97675845059922</v>
+        <v>2.108723248222373</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.54666505723534</v>
+        <v>3.988833071800743</v>
       </c>
       <c r="D3" t="n">
-        <v>32.1181406292137</v>
+        <v>5.219197852247226</v>
       </c>
       <c r="E3" t="n">
-        <v>14.21492039917519</v>
+        <v>2.309924564865969</v>
       </c>
       <c r="F3" t="n">
-        <v>12.97675845059922</v>
+        <v>2.108723248222373</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.46198338688563</v>
+        <v>3.325072300368916</v>
       </c>
       <c r="D4" t="n">
-        <v>21.9634728553543</v>
+        <v>3.569064338995073</v>
       </c>
       <c r="E4" t="n">
-        <v>14.21492039917519</v>
+        <v>2.309924564865969</v>
       </c>
       <c r="F4" t="n">
-        <v>12.97675845059922</v>
+        <v>2.108723248222373</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.72103775972912</v>
+        <v>7.104668635955982</v>
       </c>
       <c r="D5" t="n">
-        <v>47.6821676145427</v>
+        <v>7.748352237363189</v>
       </c>
       <c r="E5" t="n">
-        <v>14.21492039917519</v>
+        <v>2.309924564865969</v>
       </c>
       <c r="F5" t="n">
-        <v>12.97675845059922</v>
+        <v>2.108723248222373</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.95463887219368</v>
+        <v>7.630128816731474</v>
       </c>
       <c r="D6" t="n">
-        <v>52.08328338873439</v>
+        <v>8.463533550669338</v>
       </c>
       <c r="E6" t="n">
-        <v>14.21492039917519</v>
+        <v>2.309924564865969</v>
       </c>
       <c r="F6" t="n">
-        <v>12.97675845059922</v>
+        <v>2.108723248222373</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.74148666518394</v>
+        <v>8.732991583092391</v>
       </c>
       <c r="D7" t="n">
-        <v>53.78580372848602</v>
+        <v>8.74019310587898</v>
       </c>
       <c r="E7" t="n">
-        <v>14.21492039917519</v>
+        <v>2.309924564865969</v>
       </c>
       <c r="F7" t="n">
-        <v>12.97675845059922</v>
+        <v>2.108723248222373</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.54492011355801</v>
+        <v>7.238549518453177</v>
       </c>
       <c r="D8" t="n">
-        <v>55.713465725208</v>
+        <v>9.0534381803463</v>
       </c>
       <c r="E8" t="n">
-        <v>14.21492039917519</v>
+        <v>2.309924564865969</v>
       </c>
       <c r="F8" t="n">
-        <v>12.97675845059922</v>
+        <v>2.108723248222373</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
